--- a/client/dist/Sorce/balanceZP.xlsx
+++ b/client/dist/Sorce/balanceZP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="465">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 09.02.2025 14:55:11</t>
+    <t>Период: на 23.12.2025 16:15:12</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -62,21 +62,60 @@
     <t>ДЕСЕРТИ</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт</t>
+    <t>Желе ананас УБ 78г /56шт</t>
+  </si>
+  <si>
+    <t>Желе ананас УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе вишня УБ 78г /56шт</t>
+  </si>
+  <si>
+    <t>Желе вишня УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Какао-порошок 100г/40 УБ</t>
   </si>
   <si>
+    <t>Какао-порошок УБ 80г /48шт</t>
+  </si>
+  <si>
     <t>ДОБАВКИ</t>
   </si>
   <si>
@@ -86,60 +125,120 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
+    <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желатин УБ 25г /42шт</t>
   </si>
   <si>
+    <t>Желатин УБ 25г /42шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 100г /48шт</t>
   </si>
   <si>
+    <t>Лимонна кислота УБ 100г /48шт /</t>
+  </si>
+  <si>
+    <t>Лимонна кислота УБ 100г /48шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Лимонна кислота УБ 100г /48шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
+  </si>
+  <si>
     <t>ПРИПРАВИ</t>
   </si>
   <si>
     <t>Приправа до картоплі УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до курки УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до курки УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
+    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
+    <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до шашлику УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до шашлику УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Прованські трави УБ 10г /28шт</t>
   </si>
   <si>
+    <t>Прованські трави УБ 10г /28шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Суміш зелені УБ 10г /24шт</t>
+  </si>
+  <si>
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
+    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
+    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
     <t>Томати з часником та базиліком УБ 20г /30шт</t>
   </si>
   <si>
-    <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП 1</t>
+    <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Часник гранульований сушений УБ 15г /42шт</t>
   </si>
   <si>
+    <t>Часник гранульований сушений УБ 15г /42шт /</t>
+  </si>
+  <si>
+    <t>Часник гранульований сушений УБ 15г /42шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>СПЕЦІЇ</t>
   </si>
   <si>
@@ -164,7 +263,10 @@
     <t>Паприка мелена УБ 20г /34шт</t>
   </si>
   <si>
-    <t>Перець духм"яний УБ 20г /22шт</t>
+    <t>Перець духмяний УБ 15г /30шт</t>
+  </si>
+  <si>
+    <t>Перець духмяний УБ 20г /22шт</t>
   </si>
   <si>
     <t>Перець червоний мелений УБ 20г /32шт</t>
@@ -173,15 +275,21 @@
     <t>Перець чорний горошком УБ 20г /32шт</t>
   </si>
   <si>
-    <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
   </si>
   <si>
+    <t>Суміш перців з прянощами подрібнена УБ 30г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш перців Класична УБ 30г /24шт</t>
   </si>
   <si>
@@ -191,66 +299,72 @@
     <t>БАТОНИ</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт ДС</t>
-  </si>
-  <si>
-    <t>БАТОН ROSHEN з начинкою 43г/180</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г/180 шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Батон мол-шок карамель 40г/180/30</t>
-  </si>
-  <si>
-    <t>Батон мол-шок крем-брюле 43г/180/30</t>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>БІСКВІТИ</t>
   </si>
   <si>
-    <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт</t>
-  </si>
-  <si>
-    <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
   </si>
   <si>
+    <t>Бісквіт Рошен Празький ВКФ 300г /9шт</t>
+  </si>
+  <si>
     <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт</t>
   </si>
   <si>
-    <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>РУЛЕТ П'янка вишня ВКФ 180г /14шт</t>
   </si>
   <si>
@@ -260,18 +374,30 @@
     <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>ВАФЛІ ФАСОВАНІ</t>
   </si>
   <si>
     <t>Konafetto cocoa з начинкою крем-какао ВКФ 140г /15шт</t>
   </si>
   <si>
+    <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
+  </si>
+  <si>
     <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -293,18 +419,18 @@
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
+    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -326,12 +452,12 @@
     <t>Wafers горіх ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers какао ВКФ 72г /22шт AR /</t>
-  </si>
-  <si>
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао ККФ 72г /22шт AR /</t>
+  </si>
+  <si>
     <t>Wafers какао-молоко ККФ 216г /16шт</t>
   </si>
   <si>
@@ -341,7 +467,7 @@
     <t>Wafers лимон ВКФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers лимон ВКФ 72г /22шт AR /</t>
+    <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
@@ -353,12 +479,6 @@
     <t>Wafers молоко ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers молоко ККФ 216г /16шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Wafers молоко ККФ 216г /16шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>КАРАМЕЛЬ 200/300</t>
   </si>
   <si>
@@ -377,6 +497,9 @@
     <t>Korivka Roshen 205г/12</t>
   </si>
   <si>
+    <t>Milky Splash РЦ 150г /12пак</t>
+  </si>
+  <si>
     <t>Mintex+ Berry зі смаком лісових ягід та ментолу ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -386,13 +509,19 @@
     <t>Mintex+ зі смаком м'яти ВКФ 140г /15шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ</t>
+    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
@@ -404,21 +533,33 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -428,7 +569,7 @@
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ</t>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
@@ -437,43 +578,94 @@
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ</t>
+    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ</t>
+    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
@@ -482,24 +674,39 @@
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ RO</t>
+  </si>
+  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -524,16 +731,22 @@
     <t>Шалена бджілка ВКФ 200г /12шт</t>
   </si>
   <si>
+    <t>Шалена бджілка РЦ 200г /12шт</t>
+  </si>
+  <si>
     <t>КАРАМЕЛЬ ВАГОВА</t>
   </si>
   <si>
     <t>Beri РЦ 1кг /8пак /</t>
   </si>
   <si>
-    <t>CoffeeLike КрКФ 1кг /7пак /</t>
-  </si>
-  <si>
-    <t>Fudgenta ВКФ 0.785кг /9пак</t>
+    <t>Coconut КрКФ 1кг /7пак</t>
+  </si>
+  <si>
+    <t>CoffeeLike ВКФ 1кг /7пак</t>
+  </si>
+  <si>
+    <t>Fudgenta ВКФ 0.785кг /9пак /</t>
   </si>
   <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
@@ -542,6 +755,9 @@
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
   </si>
   <si>
+    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
+  </si>
+  <si>
     <t>Lollipops GUM Cola КрКФ 0.92кг /9шт</t>
   </si>
   <si>
@@ -551,9 +767,6 @@
     <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
   </si>
   <si>
-    <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт</t>
-  </si>
-  <si>
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
   </si>
   <si>
@@ -572,6 +785,9 @@
     <t>Mintex+ Lemon зі смаком лимону та ментолу ВКФ 1кг /9пак</t>
   </si>
   <si>
+    <t>Peppinezzz РЦ 0.9кг /6пак</t>
+  </si>
+  <si>
     <t>Roshen Butter-Milk КрКФ 1кг /8шт</t>
   </si>
   <si>
@@ -599,7 +815,7 @@
     <t>Карамелькино КрКФ 1кг /8пак /</t>
   </si>
   <si>
-    <t>Молочна крапля ВКФ 1кг /7пак</t>
+    <t>Молочна крапля ВКФ 1кг /7пак /</t>
   </si>
   <si>
     <t>Молочна крапля КрКФ 1кг /7пак /</t>
@@ -635,16 +851,10 @@
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
-    <t>Cherry Queen heart РЦ 122г /8шт</t>
-  </si>
-  <si>
-    <t>Cherry Queen heart РЦ 122г /8шт ДС</t>
-  </si>
-  <si>
-    <t>Chocolateria ВКФ 194г /8шт NEW</t>
-  </si>
-  <si>
-    <t>Chocolateria ВКФ 256г /8шт</t>
+    <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Chocolateria ВКФ 194г /8шт NEW АКЦІЯ</t>
   </si>
   <si>
     <t>Roshen Compliment ВКФ 145г /8шт</t>
@@ -653,6 +863,9 @@
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
+    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦІЯ</t>
+  </si>
+  <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
   </si>
   <si>
@@ -662,10 +875,13 @@
     <t>Shooters з ромовим лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
-    <t>Київ вечірній ККФ 176г /7шт</t>
-  </si>
-  <si>
-    <t>Київ вечірній ККФ 352г /7шт</t>
+    <t>Київ вечірній ВКФ 176г /7шт</t>
+  </si>
+  <si>
+    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
     <t>Стріла Подільска 200г/10</t>
@@ -674,6 +890,33 @@
     <t>ПЕЧИВО ТА КРЕКЕР ФАСОВАНІ</t>
   </si>
   <si>
+    <t>2 CRACK з молочно-ванільною начинкою ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>2 CRACK з шоколадною начинкою ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом та какао ВКФ 140г /12шт</t>
+  </si>
+  <si>
+    <t>Lovita Blondie Brownie з кокосом ККФ 152г /21шт</t>
+  </si>
+  <si>
+    <t>Lovita Blondie Brownie з лимоном ККФ 152г /21шт</t>
+  </si>
+  <si>
+    <t>Lovita Brownie з какао ККФ 152г /21шт</t>
+  </si>
+  <si>
+    <t>Lovita Cake Cookies з вишнево-ванільною начинкою ККФ 168г /16шт</t>
+  </si>
+  <si>
     <t>Lovita Cake Cookies з полуничною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
@@ -692,12 +935,6 @@
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies c желейною начинкою какао + вишня ККФ 135г /21шт /</t>
-  </si>
-  <si>
-    <t>Lovita Jelly Cookies c желейною начинкою какао + вишня ККФ 420г /7шт</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -719,6 +956,12 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 135г /21шт /</t>
+  </si>
+  <si>
+    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 420г /7шт</t>
+  </si>
+  <si>
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
@@ -728,30 +971,36 @@
     <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт</t>
+  </si>
+  <si>
+    <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lovita Soft Cream Cookies Peanut ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Multicake з молочно-кремовою начинкою 180г/28</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою вишня-крем ККФ 180г /28шт</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою какао 180г/28</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою какао ККФ 180г /28шт UA FP</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт</t>
+    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
   </si>
   <si>
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Multicake з начинкою чорниця-крем ККФ 180г /28шт</t>
-  </si>
-  <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
   </si>
   <si>
@@ -761,63 +1010,123 @@
     <t>До кави пряжене молоко ВКФ 185г /28шт /АКЦІЯ</t>
   </si>
   <si>
+    <t>До кави пряжене молоко ККФ 370г /24шт</t>
+  </si>
+  <si>
     <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт UA</t>
-  </si>
-  <si>
-    <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт</t>
-  </si>
-  <si>
-    <t>КРЕКЕР 2 CRACK з шоколадною начинкою ККФ 235г /14шт</t>
+    <t>ПОДАРУНКИ</t>
+  </si>
+  <si>
+    <t>ПОДАРУНКИ 2026</t>
+  </si>
+  <si>
+    <t>Н/п №10 26 Новорічний камін РЦ 665г /4шт</t>
+  </si>
+  <si>
+    <t>Н/п №11 26 Новорічний будиночок РЦ 729г /6шт</t>
+  </si>
+  <si>
+    <t>Н/п №12 26 Годівниця для птахів РЦ 918г /2шт</t>
+  </si>
+  <si>
+    <t>Н/п №7 26 Різдвяне небо РЦ 509г /6шт</t>
+  </si>
+  <si>
+    <t>Н/п №8 26 Різдвяний ярмарок РЦ 561г /4шт</t>
   </si>
   <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
-    <t>Candy Nut м"яка карамель з арахісом ВКФ 1кг /8пак PT</t>
+    <t>Boo! Bear РЦ 1кг /5пак</t>
+  </si>
+  <si>
+    <t>Boo! Bear РЦ 1кг /5пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
+  </si>
+  <si>
+    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
   </si>
   <si>
-    <t>Galaretka Roshen РЦ 2кг /5пак</t>
-  </si>
-  <si>
-    <t>Hola! Granola РЦ 0.5кг /8пак</t>
-  </si>
-  <si>
-    <t>Johnny Krocker choco ВКФ 1кг /4шт /</t>
+    <t>Flaksi какао ККФ 0.5кг /8пак</t>
+  </si>
+  <si>
+    <t>Flaksi кокос ККФ 0.5кг /8пак</t>
+  </si>
+  <si>
+    <t>Galaretka Roshen РЦ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Galaretka Roshen РЦ 1кг /9пак АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker milk ВКФ 1кг /4шт /</t>
+    <t>Johnny Krocker choco ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
+  </si>
+  <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
+  </si>
+  <si>
+    <t>Johnny Krocker milk ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Ko-Ko Choco White 1кг/5</t>
   </si>
   <si>
+    <t>Ko-Ko Choco White ВКФ 1кг /5пак АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
+  </si>
+  <si>
+    <t>KONAFETTO nero ККФ 1кг /5пак /</t>
+  </si>
+  <si>
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
   </si>
   <si>
-    <t>Sorrento ВКФ 2кг /5пак</t>
+    <t>Krock з арахісом ВКФ 1кг /8пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Milaxy ВКФ 1кг /4пак</t>
+  </si>
+  <si>
+    <t>Sorrento ВКФ 1кг /9пак</t>
   </si>
   <si>
     <t>Кара-Кум ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Кара-Кум ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
+    <t>Ліщина ВКФ 1кг /6пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Ліщина ВКФ 1кг /6пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -833,22 +1142,19 @@
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
-    <t>Ромашка ВКФ 2кг /5пак</t>
+    <t>Ромашка ВКФ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
@@ -857,94 +1163,160 @@
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Червоний мак ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Шоколапки ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
-    <t>Монблан РЦ 240г /15шт</t>
+    <t>Johnny Krocker coconut ВКФ 350г /12шт</t>
+  </si>
+  <si>
+    <t>Монблан РЦ 240г /15шт /</t>
   </si>
   <si>
     <t>ШОКОЛАД</t>
   </si>
   <si>
+    <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
+  </si>
+  <si>
+    <t>Lacmi Big Bite молочний ВКФ 200г /17шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочный ВКФ 260г /15шт</t>
-  </si>
-  <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
-    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова</t>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний ВКФ 90г /22шт</t>
+  </si>
+  <si>
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ</t>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт UA TP</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з сезамом ВКФ 90г /22шт</t>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
@@ -953,76 +1325,67 @@
     <t>Lacmi молочний з цілими лісовими горіхами ВКФ 90г /16шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з цілими лісовими горіхами ВКФ 90г /18шт /</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілими лісовими горіхами і шоколадно-карамельною начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з цілими лісовими горіхами і шоколадно-карамельною начинкою ВКФ 295г /12шт UA TP</t>
+  </si>
+  <si>
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт</t>
   </si>
   <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
+  </si>
+  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
-  </si>
-  <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ</t>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
-  </si>
-  <si>
-    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
+    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Roshen пористий білий ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP /</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт UA АКЦІЯ</t>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
     <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /</t>
@@ -1031,22 +1394,25 @@
     <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /АКЦІЯ</t>
   </si>
   <si>
-    <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
-  </si>
-  <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
   </si>
   <si>
+    <t>Roshen чорний термостійкий РЦ 80г /13шт HAL</t>
+  </si>
+  <si>
     <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт</t>
   </si>
   <si>
-    <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
   </si>
   <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
+    <t>ФІГУРКИ</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
   </si>
 </sst>
 </file>
@@ -1220,7 +1586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1273,6 +1639,12 @@
     <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1292,7 +1664,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C343"/>
+  <dimension ref="C465"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1357,7 +1729,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1365,7 +1737,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>178257</v>
+        <v>284090</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1373,7 +1745,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>20473</v>
+        <v>58717</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1381,7 +1753,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>1854</v>
+        <v>7731</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1389,7 +1761,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>362</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1397,7 +1769,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>98</v>
+        <v>560</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1405,7 +1777,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>263</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1413,7 +1785,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>501</v>
+        <v>672</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -1421,15 +1793,15 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="20" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B20" s="14" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="12" t="n">
-        <v>4429</v>
+      <c r="C20" s="11" t="n">
+        <v>368</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1437,7 +1809,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>663</v>
+        <v>859</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1445,15 +1817,15 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>727</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
       <c r="B23" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="16" t="n">
-        <v>2588</v>
+      <c r="C23" s="11" t="n">
+        <v>388</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1461,7 +1833,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1469,15 +1841,15 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="26" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B26" s="14" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="26" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B26" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="12" t="n">
-        <v>5301</v>
+      <c r="C26" s="11" t="n">
+        <v>374</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
@@ -1485,7 +1857,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>355</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1493,7 +1865,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>227</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1501,7 +1873,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>848</v>
+        <v>432</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1509,7 +1881,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>76</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
@@ -1517,7 +1889,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>109</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
@@ -1525,47 +1897,47 @@
         <v>31</v>
       </c>
       <c r="C32" s="16" t="n">
-        <v>1867</v>
-      </c>
-    </row>
-    <row r="33" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B33" s="15" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="33" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B33" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="11" t="n">
-        <v>59</v>
+      <c r="C33" s="12" t="n">
+        <v>26936</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
       <c r="B34" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>554</v>
+      <c r="C34" s="16" t="n">
+        <v>1647</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
       <c r="B35" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="11" t="n">
-        <v>210</v>
+      <c r="C35" s="16" t="n">
+        <v>3787</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="11" t="n">
-        <v>202</v>
+      <c r="C36" s="16" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
       <c r="B37" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="11" t="n">
-        <v>132</v>
+      <c r="C37" s="16" t="n">
+        <v>4403</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1573,15 +1945,15 @@
         <v>37</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>36</v>
+        <v>580</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>53</v>
+      <c r="C39" s="16" t="n">
+        <v>5308</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1589,23 +1961,23 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="41" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B41" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B41" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="12" t="n">
-        <v>8889</v>
+      <c r="C41" s="16" t="n">
+        <v>1360</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>101</v>
+      <c r="C42" s="16" t="n">
+        <v>3360</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
@@ -1613,7 +1985,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -1621,15 +1993,15 @@
         <v>43</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>56</v>
+        <v>824</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
       <c r="B45" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>231</v>
+      <c r="C45" s="16" t="n">
+        <v>1540</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1637,23 +2009,23 @@
         <v>45</v>
       </c>
       <c r="C46" s="16" t="n">
-        <v>1902</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
       <c r="B47" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="11" t="n">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="48" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B48" s="15" t="s">
+      <c r="C47" s="16" t="n">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="48" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B48" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="11" t="n">
-        <v>6</v>
+      <c r="C48" s="12" t="n">
+        <v>8699</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -1661,7 +2033,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>997</v>
+        <v>293</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1669,15 +2041,15 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>708</v>
+        <v>271</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
       <c r="B51" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="16" t="n">
-        <v>1503</v>
+      <c r="C51" s="11" t="n">
+        <v>550</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1685,15 +2057,15 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
       <c r="B53" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="16" t="n">
-        <v>2313</v>
+      <c r="C53" s="11" t="n">
+        <v>733</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -1701,7 +2073,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>218</v>
+        <v>379</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -1709,39 +2081,39 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="56" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B56" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="56" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B56" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C56" s="12" t="n">
-        <v>157784</v>
-      </c>
-    </row>
-    <row r="57" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B57" s="14" t="s">
+      <c r="C56" s="11" t="n">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="57" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B57" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="12" t="n">
-        <v>48505</v>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C57" s="11" t="n">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="58" ht="11" customHeight="true" outlineLevel="3">
       <c r="B58" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="16" t="n">
-        <v>2552</v>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C58" s="11" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59" ht="11" customHeight="true" outlineLevel="3">
       <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="16" t="n">
-        <v>2160</v>
+      <c r="C59" s="11" t="n">
+        <v>335</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1749,103 +2121,103 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>890</v>
+        <v>173</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
       <c r="B61" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="16" t="n">
-        <v>1800</v>
+      <c r="C61" s="11" t="n">
+        <v>367</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
       <c r="B62" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="16" t="n">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C62" s="11" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" ht="11" customHeight="true" outlineLevel="3">
       <c r="B63" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="16" t="n">
-        <v>3240</v>
+      <c r="C63" s="11" t="n">
+        <v>515</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="16" t="n">
-        <v>1483</v>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C64" s="11" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="16" t="n">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C65" s="11" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="16" t="n">
-        <v>17193</v>
+      <c r="C66" s="11" t="n">
+        <v>189</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="16" t="n">
-        <v>3240</v>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C67" s="11" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="16" t="n">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C68" s="11" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="16" t="n">
-        <v>1800</v>
+      <c r="C69" s="11" t="n">
+        <v>308</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="16" t="n">
-        <v>5069</v>
+      <c r="C70" s="11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="16" t="n">
-        <v>3318</v>
-      </c>
-    </row>
-    <row r="72" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B72" s="14" t="s">
+      <c r="C71" s="11" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B72" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="12" t="n">
-        <v>1287</v>
+      <c r="C72" s="11" t="n">
+        <v>991</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -1853,15 +2225,15 @@
         <v>72</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="74" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B74" s="15" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="74" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B74" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="11" t="n">
-        <v>8</v>
+      <c r="C74" s="12" t="n">
+        <v>15351</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
@@ -1869,15 +2241,15 @@
         <v>74</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>109</v>
+        <v>441</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
       <c r="B76" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="11" t="n">
-        <v>370</v>
+      <c r="C76" s="16" t="n">
+        <v>1186</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
@@ -1885,7 +2257,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>72</v>
+        <v>229</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
@@ -1893,23 +2265,23 @@
         <v>77</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>232</v>
+        <v>335</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
       <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="11" t="n">
-        <v>123</v>
+      <c r="C79" s="16" t="n">
+        <v>2510</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="11" t="n">
-        <v>93</v>
+      <c r="C80" s="16" t="n">
+        <v>1039</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -1917,23 +2289,23 @@
         <v>80</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>78</v>
+        <v>894</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
       <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="11" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B83" s="14" t="s">
+      <c r="C82" s="16" t="n">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="12" t="n">
-        <v>9057</v>
+      <c r="C83" s="11" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="84" ht="11" customHeight="true" outlineLevel="3">
@@ -1941,23 +2313,23 @@
         <v>83</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>182</v>
+        <v>419</v>
       </c>
     </row>
     <row r="85" ht="11" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="11" t="n">
-        <v>625</v>
+      <c r="C85" s="16" t="n">
+        <v>2309</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C86" s="11" t="n">
-        <v>7</v>
+      <c r="C86" s="16" t="n">
+        <v>3674</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
@@ -1965,7 +2337,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>102</v>
+        <v>270</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
@@ -1973,7 +2345,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>605</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -1981,7 +2353,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>20</v>
+        <v>690</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
@@ -1989,7 +2361,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
@@ -1997,175 +2369,175 @@
         <v>90</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="92" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B92" s="15" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="92" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B92" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="11" t="n">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="93" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B93" s="15" t="s">
+      <c r="C92" s="12" t="n">
+        <v>225373</v>
+      </c>
+    </row>
+    <row r="93" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B93" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="16" t="n">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="94" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C93" s="12" t="n">
+        <v>77900</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="95" ht="11" customHeight="true" outlineLevel="3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="96" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C95" s="16" t="n">
+        <v>7091</v>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="11" t="n">
-        <v>66</v>
+      <c r="C96" s="16" t="n">
+        <v>1878</v>
       </c>
     </row>
     <row r="97" ht="11" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="11" t="n">
-        <v>87</v>
+      <c r="C97" s="16" t="n">
+        <v>1346</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="11" t="n">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="99" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C98" s="16" t="n">
+        <v>5893</v>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="100" ht="11" customHeight="true" outlineLevel="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="101" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C100" s="16" t="n">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="102" ht="11" customHeight="true" outlineLevel="3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="true" outlineLevel="3">
       <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C102" s="16" t="n">
+        <v>9300</v>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="11" t="n">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C103" s="16" t="n">
+        <v>14190</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="true" outlineLevel="3">
       <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="11" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="105" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C104" s="16" t="n">
+        <v>3615</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="11" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="106" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C105" s="16" t="n">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="true" outlineLevel="3">
       <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="11" t="n">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="107" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C106" s="16" t="n">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="true" outlineLevel="3">
       <c r="B107" s="15" t="s">
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="108" ht="11" customHeight="true" outlineLevel="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="109" ht="11" customHeight="true" outlineLevel="3">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="true" outlineLevel="3">
       <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
       <c r="C109" s="16" t="n">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="110" ht="11" customHeight="true" outlineLevel="3">
+        <v>11501</v>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="111" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C110" s="16" t="n">
+        <v>12196</v>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="true" outlineLevel="3">
       <c r="B111" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="11" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="112" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B112" s="15" t="s">
+      <c r="C111" s="16" t="n">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="112" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B112" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="11" t="n">
-        <v>195</v>
+      <c r="C112" s="12" t="n">
+        <v>6564</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
@@ -2173,23 +2545,23 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="114" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B114" s="14" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="114" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B114" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="C114" s="12" t="n">
-        <v>15583</v>
+      <c r="C114" s="11" t="n">
+        <v>613</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
       <c r="B115" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="C115" s="11" t="n">
-        <v>13</v>
+      <c r="C115" s="16" t="n">
+        <v>1171</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
@@ -2197,7 +2569,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>74</v>
+        <v>444</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
@@ -2205,7 +2577,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>66</v>
+        <v>687</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2213,7 +2585,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>20</v>
+        <v>140</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2221,7 +2593,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>120</v>
+        <v>630</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2229,7 +2601,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>156</v>
+        <v>170</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2237,7 +2609,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>144</v>
+        <v>749</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2245,23 +2617,23 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="123" ht="11" customHeight="true" outlineLevel="3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="123" ht="22" customHeight="true" outlineLevel="3">
       <c r="B123" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="11" t="n">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="124" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B124" s="15" t="s">
+      <c r="C123" s="16" t="n">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B124" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="11" t="n">
-        <v>426</v>
+      <c r="C124" s="12" t="n">
+        <v>13357</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2269,7 +2641,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>427</v>
+        <v>263</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2277,7 +2649,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>574</v>
+        <v>293</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2285,7 +2657,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>853</v>
+        <v>347</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2293,7 +2665,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>360</v>
+        <v>37</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2301,7 +2673,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>376</v>
+        <v>277</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2309,15 +2681,15 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
       <c r="B131" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="11" t="n">
-        <v>419</v>
+      <c r="C131" s="16" t="n">
+        <v>3371</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2325,15 +2697,15 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>132</v>
+        <v>175</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
       <c r="B133" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="11" t="n">
-        <v>707</v>
+      <c r="C133" s="16" t="n">
+        <v>2169</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2341,15 +2713,15 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>247</v>
+        <v>50</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
       <c r="B135" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="11" t="n">
-        <v>192</v>
+      <c r="C135" s="16" t="n">
+        <v>2365</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2357,7 +2729,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>186</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2365,7 +2737,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>132</v>
+        <v>101</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2373,7 +2745,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>681</v>
+        <v>28</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2381,7 +2753,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>426</v>
+        <v>106</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2389,7 +2761,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>105</v>
+        <v>136</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2397,7 +2769,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>346</v>
+        <v>125</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2405,7 +2777,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>126</v>
+        <v>301</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2413,7 +2785,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>240</v>
+        <v>524</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2421,7 +2793,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>426</v>
+        <v>81</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2429,7 +2801,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>96</v>
+        <v>205</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2437,7 +2809,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>126</v>
+        <v>559</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2445,7 +2817,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>242</v>
+        <v>69</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2453,7 +2825,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>426</v>
+        <v>280</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2461,7 +2833,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>546</v>
+        <v>34</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2469,7 +2841,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>192</v>
+        <v>245</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2477,7 +2849,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>445</v>
+        <v>167</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2485,7 +2857,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>132</v>
+        <v>46</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2493,15 +2865,15 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="154" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B154" s="15" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="154" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B154" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="11" t="n">
-        <v>426</v>
+      <c r="C154" s="12" t="n">
+        <v>31430</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2509,7 +2881,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2517,15 +2889,15 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>192</v>
+        <v>113</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
       <c r="B157" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C157" s="16" t="n">
-        <v>1259</v>
+      <c r="C157" s="11" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2533,7 +2905,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>426</v>
+        <v>114</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2541,7 +2913,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>229</v>
+        <v>125</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2549,7 +2921,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2557,7 +2929,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>670</v>
+        <v>94</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2565,7 +2937,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>360</v>
+        <v>107</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2573,7 +2945,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2581,15 +2953,15 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>146</v>
+        <v>213</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
       <c r="B165" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C165" s="11" t="n">
-        <v>4</v>
+      <c r="C165" s="16" t="n">
+        <v>1151</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -2597,7 +2969,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>2</v>
+        <v>306</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2605,7 +2977,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2613,15 +2985,15 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="169" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B169" s="14" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="169" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B169" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C169" s="12" t="n">
-        <v>9829</v>
+      <c r="C169" s="11" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2629,7 +3001,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>127</v>
+        <v>73</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2637,15 +3009,15 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
       <c r="B172" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="C172" s="11" t="n">
-        <v>283</v>
+      <c r="C172" s="16" t="n">
+        <v>1837</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2653,7 +3025,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>537</v>
+        <v>260</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2661,7 +3033,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>12</v>
+        <v>86</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2669,7 +3041,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>68</v>
+        <v>546</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2677,7 +3049,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>24</v>
+        <v>207</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2685,7 +3057,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>129</v>
+        <v>84</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2693,7 +3065,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>16</v>
+        <v>746</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2701,7 +3073,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>121</v>
+        <v>193</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -2709,7 +3081,7 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>179</v>
+        <v>37</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -2717,7 +3089,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>189</v>
+        <v>89</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -2725,7 +3097,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>502</v>
+        <v>13</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -2733,7 +3105,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>128</v>
+        <v>322</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -2741,7 +3113,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>191</v>
+        <v>213</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -2749,7 +3121,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>594</v>
+        <v>565</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -2757,7 +3129,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>562</v>
+        <v>325</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -2765,7 +3137,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>145</v>
+        <v>26</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -2773,7 +3145,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>332</v>
+        <v>56</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -2781,7 +3153,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>309</v>
+        <v>618</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -2789,7 +3161,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>285</v>
+        <v>25</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -2797,7 +3169,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>609</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -2805,7 +3177,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>656</v>
+        <v>420</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -2813,15 +3185,15 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="194" ht="11" customHeight="true" outlineLevel="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="194" ht="22" customHeight="true" outlineLevel="3">
       <c r="B194" s="15" t="s">
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>33</v>
+        <v>453</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -2829,7 +3201,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>528</v>
+        <v>62</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -2837,7 +3209,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>605</v>
+        <v>20</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -2845,15 +3217,15 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="198" ht="11" customHeight="true" outlineLevel="3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="198" ht="22" customHeight="true" outlineLevel="3">
       <c r="B198" s="15" t="s">
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>853</v>
+        <v>30</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -2861,15 +3233,15 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="200" ht="11" customHeight="true" outlineLevel="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="200" ht="22" customHeight="true" outlineLevel="3">
       <c r="B200" s="15" t="s">
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>370</v>
+        <v>703</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -2877,15 +3249,15 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="202" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B202" s="14" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="202" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B202" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="C202" s="12" t="n">
-        <v>2220</v>
+      <c r="C202" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -2893,7 +3265,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>185</v>
+        <v>79</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -2901,15 +3273,15 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>435</v>
+        <v>496</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
       <c r="B205" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="11" t="n">
-        <v>539</v>
+      <c r="C205" s="16" t="n">
+        <v>1594</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -2917,7 +3289,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>24</v>
+        <v>438</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -2925,7 +3297,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>160</v>
+        <v>497</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -2933,7 +3305,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>86</v>
+        <v>31</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -2941,7 +3313,7 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>26</v>
+        <v>331</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -2949,7 +3321,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>310</v>
+        <v>255</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -2957,7 +3329,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>97</v>
+        <v>245</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -2965,7 +3337,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>5</v>
+        <v>768</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -2973,7 +3345,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>84</v>
+        <v>13</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -2981,7 +3353,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>116</v>
+        <v>377</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -2989,7 +3361,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>66</v>
+        <v>345</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -2997,7 +3369,7 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>18</v>
+        <v>845</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3005,15 +3377,15 @@
         <v>216</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="218" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B218" s="14" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="218" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B218" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="12" t="n">
-        <v>5698</v>
+      <c r="C218" s="11" t="n">
+        <v>290</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3021,7 +3393,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>67</v>
+        <v>862</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3029,7 +3401,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>13</v>
+        <v>634</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3037,7 +3409,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>22</v>
+        <v>219</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3045,7 +3417,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>279</v>
+        <v>40</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3053,7 +3425,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>301</v>
+        <v>535</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3061,79 +3433,79 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="225" ht="22" customHeight="true" outlineLevel="3">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="225" ht="11" customHeight="true" outlineLevel="3">
       <c r="B225" s="15" t="s">
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="226" ht="22" customHeight="true" outlineLevel="3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="227" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C226" s="16" t="n">
+        <v>5395</v>
+      </c>
+    </row>
+    <row r="227" ht="11" customHeight="true" outlineLevel="3">
       <c r="B227" s="15" t="s">
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="228" ht="22" customHeight="true" outlineLevel="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="228" ht="11" customHeight="true" outlineLevel="3">
       <c r="B228" s="15" t="s">
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="229" ht="22" customHeight="true" outlineLevel="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
       <c r="C229" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="230" ht="22" customHeight="true" outlineLevel="3">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="230" ht="11" customHeight="true" outlineLevel="3">
       <c r="B230" s="15" t="s">
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="231" ht="22" customHeight="true" outlineLevel="3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="231" ht="11" customHeight="true" outlineLevel="3">
       <c r="B231" s="15" t="s">
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="232" ht="22" customHeight="true" outlineLevel="3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
       <c r="C232" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="233" ht="22" customHeight="true" outlineLevel="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="233" ht="11" customHeight="true" outlineLevel="3">
       <c r="B233" s="15" t="s">
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>30</v>
+        <v>329</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3141,7 +3513,7 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3149,7 +3521,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>279</v>
+        <v>430</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3157,7 +3529,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3165,7 +3537,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>41</v>
+        <v>712</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3173,15 +3545,15 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="239" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B239" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B239" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="11" t="n">
-        <v>89</v>
+      <c r="C239" s="12" t="n">
+        <v>21533</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3189,7 +3561,7 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>229</v>
+        <v>642</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3197,7 +3569,7 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>299</v>
+        <v>145</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3205,7 +3577,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>868</v>
+        <v>913</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3213,15 +3585,15 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>7</v>
+        <v>440</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="11" t="n">
-        <v>260</v>
+      <c r="C244" s="16" t="n">
+        <v>2628</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3229,7 +3601,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>773</v>
+        <v>12</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3237,7 +3609,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>140</v>
+        <v>74</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3245,23 +3617,23 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="248" ht="22" customHeight="true" outlineLevel="3">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="248" ht="11" customHeight="true" outlineLevel="3">
       <c r="B248" s="15" t="s">
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="249" ht="22" customHeight="true" outlineLevel="3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="15" t="s">
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>1</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
@@ -3269,7 +3641,7 @@
         <v>249</v>
       </c>
       <c r="C250" s="11" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3277,15 +3649,15 @@
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="252" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B252" s="14" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="252" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="12" t="n">
-        <v>5789</v>
+      <c r="C252" s="11" t="n">
+        <v>884</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3293,7 +3665,7 @@
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>122</v>
+        <v>585</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3301,7 +3673,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>418</v>
+        <v>188</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3309,7 +3681,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>128</v>
+        <v>565</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3317,7 +3689,7 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3325,7 +3697,7 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>56</v>
+        <v>190</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3333,7 +3705,7 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>59</v>
+        <v>666</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3341,7 +3713,7 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>236</v>
+        <v>459</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3349,15 +3721,15 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>156</v>
+        <v>895</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
       <c r="B261" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="11" t="n">
-        <v>414</v>
+      <c r="C261" s="16" t="n">
+        <v>1468</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3365,7 +3737,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>58</v>
+        <v>435</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3373,7 +3745,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>43</v>
+        <v>829</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3381,7 +3753,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>415</v>
+        <v>613</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3389,31 +3761,31 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="266" ht="22" customHeight="true" outlineLevel="3">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="266" ht="11" customHeight="true" outlineLevel="3">
       <c r="B266" s="15" t="s">
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="267" ht="22" customHeight="true" outlineLevel="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="267" ht="11" customHeight="true" outlineLevel="3">
       <c r="B267" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="C267" s="11" t="n">
-        <v>4</v>
+      <c r="C267" s="16" t="n">
+        <v>1112</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
       <c r="B268" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="C268" s="11" t="n">
-        <v>1</v>
+      <c r="C268" s="16" t="n">
+        <v>1046</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3421,31 +3793,31 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="270" ht="22" customHeight="true" outlineLevel="3">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="270" ht="11" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>6</v>
+        <v>419</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
       <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="272" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C271" s="16" t="n">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="11" t="n">
-        <v>11</v>
+      <c r="C272" s="16" t="n">
+        <v>1242</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3453,15 +3825,15 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="274" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B274" s="15" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="274" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B274" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="11" t="n">
-        <v>20</v>
+      <c r="C274" s="12" t="n">
+        <v>2530</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3469,23 +3841,23 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="276" ht="22" customHeight="true" outlineLevel="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="276" ht="11" customHeight="true" outlineLevel="3">
       <c r="B276" s="15" t="s">
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>2</v>
+        <v>206</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
       <c r="B277" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="C277" s="16" t="n">
-        <v>1772</v>
+      <c r="C277" s="11" t="n">
+        <v>235</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3493,7 +3865,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>806</v>
+        <v>541</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3501,7 +3873,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>362</v>
+        <v>66</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3509,15 +3881,15 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="281" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B281" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="281" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="17" t="n">
-        <v>25</v>
+      <c r="C281" s="11" t="n">
+        <v>292</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3525,15 +3897,15 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="283" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B283" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="283" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B283" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="12" t="n">
-        <v>59791</v>
+      <c r="C283" s="11" t="n">
+        <v>233</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3541,7 +3913,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>8</v>
+        <v>199</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3549,55 +3921,55 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="286" ht="22" customHeight="true" outlineLevel="3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="286" ht="11" customHeight="true" outlineLevel="3">
       <c r="B286" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="C286" s="16" t="n">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="287" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C286" s="11" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="287" ht="11" customHeight="true" outlineLevel="3">
       <c r="B287" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="C287" s="16" t="n">
-        <v>3492</v>
-      </c>
-    </row>
-    <row r="288" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C287" s="11" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="288" ht="11" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="C288" s="16" t="n">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="289" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C288" s="11" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="289" ht="11" customHeight="true" outlineLevel="3">
       <c r="B289" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="C289" s="16" t="n">
-        <v>3351</v>
-      </c>
-    </row>
-    <row r="290" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B290" s="15" t="s">
+      <c r="C289" s="11" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="290" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B290" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="C290" s="11" t="n">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="291" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C290" s="12" t="n">
+        <v>16003</v>
+      </c>
+    </row>
+    <row r="291" ht="11" customHeight="true" outlineLevel="3">
       <c r="B291" s="15" t="s">
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -3605,7 +3977,7 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>856</v>
+        <v>172</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -3613,47 +3985,47 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>268</v>
+        <v>79</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
       <c r="B294" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="C294" s="16" t="n">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="295" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C294" s="11" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="295" ht="11" customHeight="true" outlineLevel="3">
       <c r="B295" s="15" t="s">
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="296" ht="22" customHeight="true" outlineLevel="3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="296" ht="11" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="297" ht="22" customHeight="true" outlineLevel="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="297" ht="11" customHeight="true" outlineLevel="3">
       <c r="B297" s="15" t="s">
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="298" ht="22" customHeight="true" outlineLevel="3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="298" ht="11" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="C298" s="16" t="n">
-        <v>8933</v>
+      <c r="C298" s="11" t="n">
+        <v>327</v>
       </c>
     </row>
     <row r="299" ht="22" customHeight="true" outlineLevel="3">
@@ -3661,71 +4033,71 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="300" ht="22" customHeight="true" outlineLevel="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="300" ht="11" customHeight="true" outlineLevel="3">
       <c r="B300" s="15" t="s">
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="301" ht="22" customHeight="true" outlineLevel="3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="301" ht="11" customHeight="true" outlineLevel="3">
       <c r="B301" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="C301" s="16" t="n">
-        <v>2093</v>
-      </c>
-    </row>
-    <row r="302" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C301" s="11" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="302" ht="11" customHeight="true" outlineLevel="3">
       <c r="B302" s="15" t="s">
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="303" ht="22" customHeight="true" outlineLevel="3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="303" ht="11" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="16" t="n">
-        <v>6641</v>
-      </c>
-    </row>
-    <row r="304" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C303" s="11" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="304" ht="11" customHeight="true" outlineLevel="3">
       <c r="B304" s="15" t="s">
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="305" ht="22" customHeight="true" outlineLevel="3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="306" ht="22" customHeight="true" outlineLevel="3">
       <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="16" t="n">
-        <v>1102</v>
+      <c r="C306" s="11" t="n">
+        <v>135</v>
       </c>
     </row>
     <row r="307" ht="22" customHeight="true" outlineLevel="3">
       <c r="B307" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="16" t="n">
-        <v>1816</v>
+      <c r="C307" s="11" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="308" ht="22" customHeight="true" outlineLevel="3">
@@ -3733,39 +4105,39 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="309" ht="11" customHeight="true" outlineLevel="3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="309" ht="22" customHeight="true" outlineLevel="3">
       <c r="B309" s="15" t="s">
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="310" ht="11" customHeight="true" outlineLevel="3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="310" ht="22" customHeight="true" outlineLevel="3">
       <c r="B310" s="15" t="s">
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="311" ht="11" customHeight="true" outlineLevel="3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="311" ht="22" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="312" ht="11" customHeight="true" outlineLevel="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="312" ht="22" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>253</v>
+        <v>34</v>
       </c>
     </row>
     <row r="313" ht="22" customHeight="true" outlineLevel="3">
@@ -3773,7 +4145,7 @@
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>111</v>
+        <v>170</v>
       </c>
     </row>
     <row r="314" ht="22" customHeight="true" outlineLevel="3">
@@ -3781,39 +4153,39 @@
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="315" ht="22" customHeight="true" outlineLevel="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="315" ht="11" customHeight="true" outlineLevel="3">
       <c r="B315" s="15" t="s">
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="316" ht="22" customHeight="true" outlineLevel="3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="316" ht="11" customHeight="true" outlineLevel="3">
       <c r="B316" s="15" t="s">
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>264</v>
+        <v>67</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
       <c r="B317" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="C317" s="16" t="n">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="318" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C317" s="11" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>510</v>
+        <v>376</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -3821,7 +4193,7 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>238</v>
+        <v>36</v>
       </c>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="3">
@@ -3829,23 +4201,23 @@
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="11" t="n">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="322" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C321" s="16" t="n">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="11" t="n">
-        <v>25</v>
+      <c r="C322" s="16" t="n">
+        <v>1885</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
@@ -3853,23 +4225,23 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="324" ht="22" customHeight="true" outlineLevel="3">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="324" ht="11" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="C324" s="16" t="n">
-        <v>2235</v>
+      <c r="C324" s="11" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="11" t="n">
-        <v>286</v>
+      <c r="C325" s="16" t="n">
+        <v>1414</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
@@ -3877,7 +4249,7 @@
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>292</v>
+        <v>151</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
@@ -3885,7 +4257,7 @@
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -3893,111 +4265,111 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="329" ht="22" customHeight="true" outlineLevel="3">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>458</v>
+        <v>742</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="C330" s="11" t="n">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="331" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C330" s="16" t="n">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="331" ht="11" customHeight="true" outlineLevel="3">
       <c r="B331" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="C331" s="11" t="n">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="332" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C331" s="16" t="n">
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="332" ht="22" customHeight="true" outlineLevel="3">
       <c r="B332" s="15" t="s">
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="333" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B333" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="333" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B333" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="11" t="n">
+      <c r="C333" s="17" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="334" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B334" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="C334" s="17" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="335" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B335" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="C335" s="11" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="336" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B336" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="C336" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B337" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="C337" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="338" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B338" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="C338" s="11" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="339" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B339" s="19" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="334" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B334" s="15" t="s">
-        <v>333</v>
-      </c>
-      <c r="C334" s="11" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="335" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B335" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="C335" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="336" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B336" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="C336" s="16" t="n">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="337" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B337" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="C337" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="338" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B338" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="C338" s="11" t="n">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="339" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B339" s="15" t="s">
-        <v>338</v>
-      </c>
       <c r="C339" s="11" t="n">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="340" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B340" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="340" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B340" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="11" t="n">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="341" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C340" s="12" t="n">
+        <v>19230</v>
+      </c>
+    </row>
+    <row r="341" ht="11" customHeight="true" outlineLevel="3">
       <c r="B341" s="15" t="s">
         <v>340</v>
       </c>
-      <c r="C341" s="16" t="n">
-        <v>5837</v>
+      <c r="C341" s="11" t="n">
+        <v>754</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
@@ -4005,15 +4377,991 @@
         <v>341</v>
       </c>
       <c r="C342" s="16" t="n">
-        <v>2194</v>
-      </c>
-    </row>
-    <row r="343" ht="22" customHeight="true" outlineLevel="3">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="343" ht="11" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
       <c r="C343" s="16" t="n">
-        <v>2485</v>
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="344" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B344" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="C344" s="16" t="n">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="345" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B345" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="C345" s="16" t="n">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="346" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B346" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="C346" s="11" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="347" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B347" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="C347" s="11" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="348" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B348" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="C348" s="11" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="349" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B349" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="C349" s="11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B350" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="C350" s="11" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="351" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B351" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="C351" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="352" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B352" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="C352" s="11" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="353" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B353" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="C353" s="11" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="354" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B354" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="C354" s="11" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="355" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B355" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="C355" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B356" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="C356" s="11" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="357" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B357" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="C357" s="11" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="358" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B358" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="C358" s="11" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="359" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B359" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="C359" s="11" t="n">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B360" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="C360" s="11" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="361" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B361" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="C361" s="11" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B362" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="C362" s="11" t="n">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="363" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B363" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="C363" s="11" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="364" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B364" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="C364" s="11" t="n">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="365" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B365" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="C365" s="11" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="366" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B366" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="C366" s="11" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="367" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B367" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="C367" s="11" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="368" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B368" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C368" s="11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="369" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B369" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="C369" s="11" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="370" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B370" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="C370" s="11" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="371" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B371" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="C371" s="11" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="372" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B372" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="C372" s="11" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="373" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B373" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="C373" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="374" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B374" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="C374" s="11" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="375" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B375" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="C375" s="11" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="376" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B376" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="C376" s="11" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="377" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B377" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="C377" s="16" t="n">
+        <v>3951</v>
+      </c>
+    </row>
+    <row r="378" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B378" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="C378" s="11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="379" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B379" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="C379" s="16" t="n">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="380" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B380" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="C380" s="16" t="n">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="381" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B381" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="C381" s="11" t="n">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="382" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B382" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="C382" s="11" t="n">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="383" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B383" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="C383" s="11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="384" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B384" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="C384" s="11" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="385" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B385" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="C385" s="17" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="386" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B386" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="C386" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="387" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B387" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="C387" s="11" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="388" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B388" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="C388" s="12" t="n">
+        <v>36545</v>
+      </c>
+    </row>
+    <row r="389" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B389" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="C389" s="11" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="390" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B390" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="C390" s="11" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="391" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B391" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="C391" s="11" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="392" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B392" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="C392" s="11" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="393" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B393" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="C393" s="11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="394" ht="33" customHeight="true" outlineLevel="3">
+      <c r="B394" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="C394" s="16" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="395" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B395" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="C395" s="11" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="396" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B396" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="C396" s="11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="397" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B397" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="C397" s="11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="398" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B398" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="C398" s="11" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="399" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B399" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="C399" s="11" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="400" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B400" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="C400" s="11" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="401" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B401" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="C401" s="11" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="402" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B402" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="C402" s="11" t="n">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="403" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B403" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="C403" s="11" t="n">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="404" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B404" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="C404" s="11" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="405" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B405" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="C405" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="406" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B406" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="C406" s="11" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="407" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B407" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="C407" s="11" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="408" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B408" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="C408" s="11" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="409" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B409" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="C409" s="16" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="410" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B410" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C410" s="11" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="411" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B411" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="C411" s="11" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="412" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B412" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="C412" s="11" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="413" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B413" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="C413" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="414" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B414" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="C414" s="16" t="n">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="415" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B415" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="C415" s="11" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="416" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B416" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="C416" s="11" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="417" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B417" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="C417" s="16" t="n">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="418" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B418" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="C418" s="11" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="419" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B419" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C419" s="11" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="420" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B420" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="C420" s="11" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="421" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B421" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="C421" s="11" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="422" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B422" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="C422" s="11" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="423" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B423" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="C423" s="11" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="424" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B424" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="C424" s="11" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="425" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B425" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="C425" s="11" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="426" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B426" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="C426" s="11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="427" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B427" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="C427" s="11" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="428" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B428" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="C428" s="11" t="n">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="429" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B429" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="C429" s="11" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="430" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B430" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="C430" s="11" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="431" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B431" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="C431" s="11" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="432" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B432" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="C432" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="433" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B433" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="C433" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="434" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B434" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="C434" s="11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="435" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B435" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="C435" s="11" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="436" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B436" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="C436" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="437" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B437" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="C437" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="438" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B438" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="C438" s="11" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="439" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B439" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="C439" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="440" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B440" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="C440" s="11" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="441" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B441" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C441" s="11" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="442" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B442" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="C442" s="11" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="443" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B443" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="C443" s="16" t="n">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="444" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B444" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="C444" s="16" t="n">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="445" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B445" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="C445" s="11" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="446" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B446" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="C446" s="16" t="n">
+        <v>3148</v>
+      </c>
+    </row>
+    <row r="447" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B447" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="C447" s="16" t="n">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="448" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B448" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="C448" s="11" t="n">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="449" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B449" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="C449" s="16" t="n">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="450" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B450" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="C450" s="11" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="451" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B451" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="C451" s="11" t="n">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="452" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B452" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="C452" s="11" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="453" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B453" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="C453" s="16" t="n">
+        <v>3390</v>
+      </c>
+    </row>
+    <row r="454" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B454" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="C454" s="11" t="n">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="455" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B455" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="C455" s="16" t="n">
+        <v>3226</v>
+      </c>
+    </row>
+    <row r="456" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B456" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="C456" s="11" t="n">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="457" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B457" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="C457" s="11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="458" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B458" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="C458" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="459" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B459" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="C459" s="11" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="460" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B460" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="C460" s="11" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="461" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B461" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="C461" s="11" t="n">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="462" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B462" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="C462" s="11" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="463" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B463" s="18" t="s">
+        <v>462</v>
+      </c>
+      <c r="C463" s="17" t="n">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="464" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B464" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="C464" s="11" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="465" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B465" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="C465" s="11" t="n">
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/client/dist/Sorce/balanceZP.xlsx
+++ b/client/dist/Sorce/balanceZP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="377">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 23.12.2025 16:15:12</t>
+    <t>Период: на 23.02.2026 11:15:12</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -62,55 +62,34 @@
     <t>ДЕСЕРТИ</t>
   </si>
   <si>
+    <t>Lacmi Гарячий шоколад УБ 20г /90шт</t>
+  </si>
+  <si>
     <t>Желе ананас УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе ананас УБ 78г /56шт АКЦІЯ ВІП</t>
+    <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
     <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе вишня УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
     <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Желе ківі УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Какао-порошок 100г/40 УБ</t>
+    <t>Какао-порошок 22% УБ 60г /26шт</t>
   </si>
   <si>
     <t>Какао-порошок УБ 80г /48шт</t>
@@ -125,6 +104,9 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
+    <t>Ванільний цукор УБ 35г /36шт</t>
+  </si>
+  <si>
     <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -134,111 +116,84 @@
     <t>Желатин УБ 25г /42шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 100г /48шт</t>
   </si>
   <si>
     <t>Лимонна кислота УБ 100г /48шт /</t>
   </si>
   <si>
-    <t>Лимонна кислота УБ 100г /48шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Лимонна кислота УБ 100г /48шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
     <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
   </si>
   <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /</t>
+  </si>
+  <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /АКЦІЯ</t>
+  </si>
+  <si>
     <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт /</t>
+  </si>
+  <si>
     <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт /</t>
+  </si>
+  <si>
     <t>ПРИПРАВИ</t>
   </si>
   <si>
     <t>Приправа до картоплі УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до курки УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до курки УБ 25г /34шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
-    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
-    <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до шашлику УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до шашлику УБ 25г /34шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Прованські трави УБ 10г /28шт</t>
   </si>
   <si>
-    <t>Прованські трави УБ 10г /28шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш зелені УБ 10г /24шт</t>
   </si>
   <si>
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
-    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
-    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
     <t>Томати з часником та базиліком УБ 20г /30шт</t>
   </si>
   <si>
-    <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Часник гранульований сушений УБ 15г /42шт</t>
   </si>
   <si>
     <t>Часник гранульований сушений УБ 15г /42шт /</t>
   </si>
   <si>
-    <t>Часник гранульований сушений УБ 15г /42шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>СПЕЦІЇ</t>
   </si>
   <si>
@@ -278,18 +233,9 @@
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
-    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
   </si>
   <si>
-    <t>Суміш перців з прянощами подрібнена УБ 30г /24шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш перців Класична УБ 30г /24шт</t>
   </si>
   <si>
@@ -302,30 +248,33 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN Truffle Sparkling Wine ВКФ 41г /180шт</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова накладна</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -338,24 +287,18 @@
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>БІСКВІТИ</t>
   </si>
   <si>
+    <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт</t>
+  </si>
+  <si>
     <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
   </si>
   <si>
@@ -374,21 +317,12 @@
     <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>ВАФЛІ ФАСОВАНІ</t>
   </si>
   <si>
@@ -401,9 +335,6 @@
     <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>KONAFETTO з горіховою начинкою ВКФ 140г /15шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Konafetto з кокосовою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -413,36 +344,45 @@
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП</t>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
   </si>
   <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch какао ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers горіх ВКФ 216г /16шт</t>
   </si>
   <si>
@@ -467,15 +407,15 @@
     <t>Wafers лимон ВКФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers лимон ВКФ 72г /22шт AR /</t>
+  </si>
+  <si>
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
   </si>
   <si>
-    <t>Wafers молоко ВКФ 72г /22шт AR /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Wafers молоко ККФ 216г /16шт</t>
   </si>
   <si>
@@ -518,10 +458,7 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Cactus ВКФ 165г /14шт</t>
   </si>
   <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
@@ -530,42 +467,18 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -575,60 +488,57 @@
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ</t>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -638,81 +548,51 @@
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
-  </si>
-  <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Rabbits ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ RO</t>
   </si>
   <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Бім-Бом РЦ 200г /11шт</t>
   </si>
   <si>
@@ -746,15 +626,15 @@
     <t>CoffeeLike ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>CoffeeLike КрКФ 1кг /7пак /</t>
+  </si>
+  <si>
     <t>Fudgenta ВКФ 0.785кг /9пак /</t>
   </si>
   <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
   </si>
   <si>
-    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
   </si>
   <si>
@@ -854,7 +734,10 @@
     <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Chocolateria ВКФ 194г /8шт NEW АКЦІЯ</t>
+    <t>Chocolateria ВКФ 194г /8шт NEW</t>
+  </si>
+  <si>
+    <t>Chocolateria ВКФ 256г /8шт</t>
   </si>
   <si>
     <t>Roshen Compliment ВКФ 145г /8шт</t>
@@ -863,9 +746,6 @@
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
-    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
   </si>
   <si>
@@ -932,9 +812,6 @@
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт</t>
   </si>
   <si>
-    <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -950,9 +827,6 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
   </si>
   <si>
@@ -968,15 +842,9 @@
     <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies Peanut ККФ 127г /18шт</t>
   </si>
   <si>
@@ -995,61 +863,25 @@
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
   </si>
   <si>
     <t>До кави пряжене молоко ВКФ 185г /28шт /</t>
   </si>
   <si>
-    <t>До кави пряжене молоко ВКФ 185г /28шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>До кави пряжене молоко ККФ 370г /24шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
-  </si>
-  <si>
-    <t>ПОДАРУНКИ</t>
-  </si>
-  <si>
-    <t>ПОДАРУНКИ 2026</t>
-  </si>
-  <si>
-    <t>Н/п №10 26 Новорічний камін РЦ 665г /4шт</t>
-  </si>
-  <si>
-    <t>Н/п №11 26 Новорічний будиночок РЦ 729г /6шт</t>
-  </si>
-  <si>
-    <t>Н/п №12 26 Годівниця для птахів РЦ 918г /2шт</t>
-  </si>
-  <si>
-    <t>Н/п №7 26 Різдвяне небо РЦ 509г /6шт</t>
-  </si>
-  <si>
-    <t>Н/п №8 26 Різдвяний ярмарок РЦ 561г /4шт</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
     <t>Boo! Bear РЦ 1кг /5пак</t>
   </si>
   <si>
-    <t>Boo! Bear РЦ 1кг /5пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
   </si>
   <si>
-    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
+    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
@@ -1064,45 +896,27 @@
     <t>Galaretka Roshen РЦ 1кг /9пак</t>
   </si>
   <si>
-    <t>Galaretka Roshen РЦ 1кг /9пак АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker choco ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
   </si>
   <si>
-    <t>Johnny Krocker coconut ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker milk ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Ko-Ko Choco White 1кг/5</t>
   </si>
   <si>
-    <t>Ko-Ko Choco White ВКФ 1кг /5пак АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
-  </si>
-  <si>
-    <t>KONAFETTO nero ККФ 1кг /5пак /</t>
+    <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
+  </si>
+  <si>
+    <t>KONAFETTO nero ККФ 1кг /5пак HAL</t>
   </si>
   <si>
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
   </si>
   <si>
-    <t>Krock з арахісом ВКФ 1кг /8пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Milaxy ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1112,21 +926,18 @@
     <t>Кара-Кум ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>Кара-Кум ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+    <t>Кара-Кум ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
-    <t>Ліщина ВКФ 1кг /6пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>Ліщина ВКФ 1кг /6пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -1142,18 +953,24 @@
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
-    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
-  </si>
-  <si>
     <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -1169,9 +986,6 @@
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>Шоколапки ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
@@ -1187,91 +1001,52 @@
     <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочний ВКФ 200г /17шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
   </si>
   <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
-  </si>
-  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
-  </si>
-  <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
-    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт UA TP</t>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова UA</t>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова UA</t>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
@@ -1280,21 +1055,12 @@
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
@@ -1313,12 +1079,6 @@
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
@@ -1334,28 +1094,25 @@
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
+    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
@@ -1364,34 +1121,22 @@
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
-    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /</t>
-  </si>
-  <si>
-    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /АКЦІЯ</t>
+    <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
@@ -1404,15 +1149,6 @@
   </si>
   <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
-  </si>
-  <si>
-    <t>ФІГУРКИ</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
   </si>
 </sst>
 </file>
@@ -1586,7 +1322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1639,12 +1375,6 @@
     <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1664,7 +1394,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C465"/>
+  <dimension ref="C377"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1729,7 +1459,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>159</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1737,7 +1467,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>284090</v>
+        <v>299812</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1745,7 +1475,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>58717</v>
+        <v>59493</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1753,7 +1483,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>7731</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1761,7 +1491,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>340</v>
+        <v>740</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1769,15 +1499,15 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>560</v>
+        <v>459</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
       <c r="B17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>24</v>
+      <c r="C17" s="16" t="n">
+        <v>1184</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1785,7 +1515,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>672</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -1793,7 +1523,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>245</v>
+        <v>977</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1801,7 +1531,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>368</v>
+        <v>805</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1809,7 +1539,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>859</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1817,7 +1547,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>24</v>
+        <v>797</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1825,7 +1555,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>388</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1833,7 +1563,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>208</v>
+        <v>645</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1841,31 +1571,31 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="26" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B26" s="15" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="26" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B26" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>374</v>
+      <c r="C26" s="12" t="n">
+        <v>19205</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
       <c r="B27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>168</v>
+      <c r="C27" s="16" t="n">
+        <v>2389</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
       <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>65</v>
+      <c r="C28" s="16" t="n">
+        <v>5303</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1873,39 +1603,39 @@
         <v>28</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>432</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
       <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="11" t="n">
-        <v>131</v>
+      <c r="C30" s="16" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>68</v>
+      <c r="C31" s="16" t="n">
+        <v>3114</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="16" t="n">
-        <v>2428</v>
-      </c>
-    </row>
-    <row r="33" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B33" s="14" t="s">
+      <c r="C32" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="12" t="n">
-        <v>26936</v>
+      <c r="C33" s="11" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -1913,7 +1643,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>1647</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1921,23 +1651,23 @@
         <v>34</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>3787</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="16" t="n">
-        <v>1100</v>
+      <c r="C36" s="11" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
       <c r="B37" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="16" t="n">
-        <v>4403</v>
+      <c r="C37" s="11" t="n">
+        <v>567</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1945,15 +1675,15 @@
         <v>37</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>580</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="16" t="n">
-        <v>5308</v>
+      <c r="C39" s="11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1961,39 +1691,39 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>28</v>
+        <v>607</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
       <c r="B41" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="16" t="n">
-        <v>1360</v>
+      <c r="C41" s="11" t="n">
+        <v>124</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="16" t="n">
-        <v>3360</v>
-      </c>
-    </row>
-    <row r="43" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B43" s="15" t="s">
+      <c r="C42" s="11" t="n">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="43" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B43" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>1</v>
+      <c r="C43" s="12" t="n">
+        <v>15697</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>824</v>
+      <c r="C44" s="16" t="n">
+        <v>1528</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -2001,15 +1731,15 @@
         <v>44</v>
       </c>
       <c r="C45" s="16" t="n">
-        <v>1540</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
       <c r="B46" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="16" t="n">
-        <v>1460</v>
+      <c r="C46" s="11" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -2017,15 +1747,15 @@
         <v>46</v>
       </c>
       <c r="C47" s="16" t="n">
-        <v>1538</v>
-      </c>
-    </row>
-    <row r="48" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B48" s="14" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="48" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B48" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="12" t="n">
-        <v>8699</v>
+      <c r="C48" s="11" t="n">
+        <v>956</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -2033,7 +1763,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>293</v>
+        <v>341</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -2041,7 +1771,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>271</v>
+        <v>222</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -2049,7 +1779,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>550</v>
+        <v>832</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -2057,7 +1787,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>98</v>
+        <v>578</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -2065,23 +1795,23 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>733</v>
+        <v>584</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
       <c r="B54" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="11" t="n">
-        <v>379</v>
+      <c r="C54" s="16" t="n">
+        <v>1118</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
       <c r="B55" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="11" t="n">
-        <v>174</v>
+      <c r="C55" s="16" t="n">
+        <v>1120</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -2089,7 +1819,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>960</v>
+        <v>953</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -2097,23 +1827,23 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>647</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
       <c r="B58" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="11" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="59" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B59" s="15" t="s">
+      <c r="C58" s="16" t="n">
+        <v>4975</v>
+      </c>
+    </row>
+    <row r="59" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B59" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="11" t="n">
-        <v>335</v>
+      <c r="C59" s="12" t="n">
+        <v>17972</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -2121,7 +1851,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>173</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2129,7 +1859,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>367</v>
+        <v>877</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -2137,23 +1867,23 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>83</v>
+        <v>872</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
       <c r="B63" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="11" t="n">
-        <v>515</v>
+      <c r="C63" s="16" t="n">
+        <v>1305</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="11" t="n">
-        <v>75</v>
+      <c r="C64" s="16" t="n">
+        <v>2001</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -2161,23 +1891,23 @@
         <v>64</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>108</v>
+        <v>782</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="11" t="n">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C66" s="16" t="n">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="11" t="n">
-        <v>213</v>
+      <c r="C67" s="16" t="n">
+        <v>1783</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
@@ -2185,7 +1915,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>381</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
@@ -2193,23 +1923,23 @@
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>308</v>
+        <v>514</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="11" t="n">
-        <v>4</v>
+      <c r="C70" s="16" t="n">
+        <v>1402</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="11" t="n">
-        <v>43</v>
+      <c r="C71" s="16" t="n">
+        <v>5971</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -2217,7 +1947,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>991</v>
+        <v>286</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -2225,55 +1955,55 @@
         <v>72</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="74" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B74" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="74" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B74" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C74" s="12" t="n">
-        <v>15351</v>
-      </c>
-    </row>
-    <row r="75" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B75" s="15" t="s">
+        <v>240319</v>
+      </c>
+    </row>
+    <row r="75" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B75" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="11" t="n">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="76" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C75" s="12" t="n">
+        <v>89465</v>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="true" outlineLevel="3">
       <c r="B76" s="15" t="s">
         <v>75</v>
       </c>
       <c r="C76" s="16" t="n">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="77" ht="11" customHeight="true" outlineLevel="3">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="true" outlineLevel="3">
       <c r="B77" s="15" t="s">
         <v>76</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="78" ht="11" customHeight="true" outlineLevel="3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="true" outlineLevel="3">
       <c r="B78" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="11" t="n">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="79" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C78" s="16" t="n">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="true" outlineLevel="3">
       <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="16" t="n">
-        <v>2510</v>
+      <c r="C79" s="11" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
@@ -2281,15 +2011,15 @@
         <v>79</v>
       </c>
       <c r="C80" s="16" t="n">
-        <v>1039</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="11" t="n">
-        <v>894</v>
+      <c r="C81" s="16" t="n">
+        <v>4848</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
@@ -2297,127 +2027,127 @@
         <v>81</v>
       </c>
       <c r="C82" s="16" t="n">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="3">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="true" outlineLevel="3">
       <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C83" s="16" t="n">
+        <v>4430</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="true" outlineLevel="3">
       <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="11" t="n">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="85" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C84" s="16" t="n">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
       <c r="C85" s="16" t="n">
-        <v>2309</v>
-      </c>
-    </row>
-    <row r="86" ht="11" customHeight="true" outlineLevel="3">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
       <c r="C86" s="16" t="n">
-        <v>3674</v>
-      </c>
-    </row>
-    <row r="87" ht="11" customHeight="true" outlineLevel="3">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="88" ht="11" customHeight="true" outlineLevel="3">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="89" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C88" s="16" t="n">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="11" t="n">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="90" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C89" s="16" t="n">
+        <v>4425</v>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="91" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C90" s="16" t="n">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="true" outlineLevel="3">
       <c r="B91" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="11" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="92" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B92" s="13" t="s">
+      <c r="C91" s="16" t="n">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="92" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B92" s="14" t="s">
         <v>91</v>
       </c>
       <c r="C92" s="12" t="n">
-        <v>225373</v>
-      </c>
-    </row>
-    <row r="93" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B93" s="14" t="s">
+        <v>5770</v>
+      </c>
+    </row>
+    <row r="93" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B93" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="12" t="n">
-        <v>77900</v>
-      </c>
-    </row>
-    <row r="94" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C93" s="11" t="n">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="94" ht="11" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="95" ht="22" customHeight="true" outlineLevel="3">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="95" ht="11" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="16" t="n">
-        <v>7091</v>
-      </c>
-    </row>
-    <row r="96" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C95" s="11" t="n">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="96" ht="11" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
       <c r="C96" s="16" t="n">
-        <v>1878</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="97" ht="11" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="16" t="n">
-        <v>1346</v>
+      <c r="C97" s="11" t="n">
+        <v>379</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
@@ -2425,119 +2155,119 @@
         <v>97</v>
       </c>
       <c r="C98" s="16" t="n">
-        <v>5893</v>
-      </c>
-    </row>
-    <row r="99" ht="22" customHeight="true" outlineLevel="3">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="99" ht="11" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="100" ht="22" customHeight="true" outlineLevel="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="100" ht="11" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="16" t="n">
-        <v>1605</v>
-      </c>
-    </row>
-    <row r="101" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C100" s="11" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="101" ht="11" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="102" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B102" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="102" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B102" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="16" t="n">
-        <v>9300</v>
-      </c>
-    </row>
-    <row r="103" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C102" s="12" t="n">
+        <v>55216</v>
+      </c>
+    </row>
+    <row r="103" ht="11" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
       <c r="C103" s="16" t="n">
-        <v>14190</v>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="true" outlineLevel="3">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="104" ht="11" customHeight="true" outlineLevel="3">
       <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="16" t="n">
-        <v>3615</v>
-      </c>
-    </row>
-    <row r="105" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C104" s="11" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105" ht="11" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
       <c r="C105" s="16" t="n">
-        <v>3630</v>
-      </c>
-    </row>
-    <row r="106" ht="22" customHeight="true" outlineLevel="3">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="106" ht="11" customHeight="true" outlineLevel="3">
       <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="16" t="n">
-        <v>2110</v>
-      </c>
-    </row>
-    <row r="107" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C106" s="11" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="107" ht="11" customHeight="true" outlineLevel="3">
       <c r="B107" s="15" t="s">
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="108" ht="22" customHeight="true" outlineLevel="3">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="108" ht="11" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="11" t="n">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="109" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C108" s="16" t="n">
+        <v>17900</v>
+      </c>
+    </row>
+    <row r="109" ht="11" customHeight="true" outlineLevel="3">
       <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
       <c r="C109" s="16" t="n">
-        <v>11501</v>
-      </c>
-    </row>
-    <row r="110" ht="22" customHeight="true" outlineLevel="3">
+        <v>16168</v>
+      </c>
+    </row>
+    <row r="110" ht="11" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
       <c r="C110" s="16" t="n">
-        <v>12196</v>
-      </c>
-    </row>
-    <row r="111" ht="22" customHeight="true" outlineLevel="3">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="111" ht="11" customHeight="true" outlineLevel="3">
       <c r="B111" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C111" s="16" t="n">
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="112" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B112" s="14" t="s">
+        <v>9750</v>
+      </c>
+    </row>
+    <row r="112" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B112" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="12" t="n">
-        <v>6564</v>
+      <c r="C112" s="11" t="n">
+        <v>107</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
@@ -2545,7 +2275,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>462</v>
+        <v>493</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2553,15 +2283,15 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>613</v>
+        <v>439</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
       <c r="B115" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="C115" s="16" t="n">
-        <v>1171</v>
+      <c r="C115" s="11" t="n">
+        <v>155</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
@@ -2569,7 +2299,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>444</v>
+        <v>478</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
@@ -2577,7 +2307,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>687</v>
+        <v>348</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2585,7 +2315,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>140</v>
+        <v>101</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2593,7 +2323,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>630</v>
+        <v>428</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2601,15 +2331,15 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="121" ht="11" customHeight="true" outlineLevel="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="true" outlineLevel="3">
       <c r="B121" s="15" t="s">
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>749</v>
+        <v>466</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2617,23 +2347,23 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="123" ht="22" customHeight="true" outlineLevel="3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="123" ht="11" customHeight="true" outlineLevel="3">
       <c r="B123" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="16" t="n">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="124" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B124" s="14" t="s">
+      <c r="C123" s="11" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B124" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="12" t="n">
-        <v>13357</v>
+      <c r="C124" s="11" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2641,7 +2371,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>263</v>
+        <v>351</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2649,7 +2379,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>293</v>
+        <v>556</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2657,7 +2387,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>347</v>
+        <v>138</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2665,7 +2395,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>37</v>
+        <v>138</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2673,7 +2403,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>277</v>
+        <v>33</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2681,15 +2411,15 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>367</v>
+        <v>96</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
       <c r="B131" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="16" t="n">
-        <v>3371</v>
+      <c r="C131" s="11" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2697,31 +2427,31 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>175</v>
+        <v>340</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
       <c r="B133" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="16" t="n">
-        <v>2169</v>
-      </c>
-    </row>
-    <row r="134" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B134" s="15" t="s">
+      <c r="C133" s="11" t="n">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="134" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B134" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="11" t="n">
-        <v>50</v>
+      <c r="C134" s="12" t="n">
+        <v>21033</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
       <c r="B135" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="16" t="n">
-        <v>2365</v>
+      <c r="C135" s="11" t="n">
+        <v>182</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2729,7 +2459,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2737,7 +2467,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>101</v>
+        <v>40</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2745,7 +2475,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2753,7 +2483,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2761,7 +2491,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>136</v>
+        <v>97</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2769,7 +2499,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2777,7 +2507,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>301</v>
+        <v>75</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2785,7 +2515,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>524</v>
+        <v>72</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2793,7 +2523,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2801,7 +2531,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>205</v>
+        <v>639</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2809,7 +2539,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>559</v>
+        <v>177</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2817,7 +2547,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>69</v>
+        <v>140</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2825,7 +2555,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>280</v>
+        <v>757</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2833,7 +2563,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>34</v>
+        <v>715</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2841,7 +2571,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>245</v>
+        <v>219</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2849,7 +2579,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>167</v>
+        <v>104</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2857,7 +2587,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>46</v>
+        <v>848</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2865,15 +2595,15 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="154" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B154" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="154" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B154" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="12" t="n">
-        <v>31430</v>
+      <c r="C154" s="11" t="n">
+        <v>994</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2881,7 +2611,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2889,7 +2619,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>113</v>
+        <v>339</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2897,7 +2627,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2905,7 +2635,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>114</v>
+        <v>349</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2913,7 +2643,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>125</v>
+        <v>350</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2921,7 +2651,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>121</v>
+        <v>61</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2929,47 +2659,47 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="162" ht="11" customHeight="true" outlineLevel="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="162" ht="22" customHeight="true" outlineLevel="3">
       <c r="B162" s="15" t="s">
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="163" ht="11" customHeight="true" outlineLevel="3">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="163" ht="22" customHeight="true" outlineLevel="3">
       <c r="B163" s="15" t="s">
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="164" ht="11" customHeight="true" outlineLevel="3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="164" ht="22" customHeight="true" outlineLevel="3">
       <c r="B164" s="15" t="s">
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>213</v>
+        <v>510</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
       <c r="B165" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C165" s="16" t="n">
-        <v>1151</v>
+      <c r="C165" s="11" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
       <c r="B166" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="11" t="n">
-        <v>306</v>
+      <c r="C166" s="16" t="n">
+        <v>1258</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2977,23 +2707,23 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="168" ht="11" customHeight="true" outlineLevel="3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="168" ht="22" customHeight="true" outlineLevel="3">
       <c r="B168" s="15" t="s">
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="169" ht="11" customHeight="true" outlineLevel="3">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="169" ht="22" customHeight="true" outlineLevel="3">
       <c r="B169" s="15" t="s">
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>220</v>
+        <v>117</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -3001,23 +2731,23 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
       <c r="B171" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="11" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="172" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C171" s="16" t="n">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="172" ht="22" customHeight="true" outlineLevel="3">
       <c r="B172" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="C172" s="16" t="n">
-        <v>1837</v>
+      <c r="C172" s="11" t="n">
+        <v>276</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -3025,7 +2755,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>260</v>
+        <v>134</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -3033,7 +2763,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>86</v>
+        <v>228</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -3041,7 +2771,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>546</v>
+        <v>220</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -3049,7 +2779,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>207</v>
+        <v>161</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -3057,7 +2787,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>84</v>
+        <v>220</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -3065,7 +2795,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>746</v>
+        <v>171</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -3073,7 +2803,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>193</v>
+        <v>39</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -3081,7 +2811,7 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>37</v>
+        <v>387</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -3089,7 +2819,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>89</v>
+        <v>167</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -3097,7 +2827,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>13</v>
+        <v>280</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -3105,7 +2835,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>322</v>
+        <v>140</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -3113,7 +2843,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -3121,7 +2851,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>565</v>
+        <v>279</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -3129,7 +2859,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>325</v>
+        <v>174</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -3137,7 +2867,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>26</v>
+        <v>73</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -3145,15 +2875,15 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>56</v>
+        <v>241</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="11" t="n">
-        <v>618</v>
+      <c r="C189" s="16" t="n">
+        <v>3296</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -3161,7 +2891,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>25</v>
+        <v>201</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -3169,7 +2899,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>20</v>
+        <v>143</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -3177,7 +2907,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>420</v>
+        <v>36</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -3185,15 +2915,15 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="194" ht="22" customHeight="true" outlineLevel="3">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="194" ht="11" customHeight="true" outlineLevel="3">
       <c r="B194" s="15" t="s">
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>453</v>
+        <v>141</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -3201,7 +2931,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>62</v>
+        <v>282</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -3209,7 +2939,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -3217,31 +2947,31 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="198" ht="22" customHeight="true" outlineLevel="3">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="198" ht="11" customHeight="true" outlineLevel="3">
       <c r="B198" s="15" t="s">
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="199" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B199" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B199" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="C199" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="200" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C199" s="12" t="n">
+        <v>13463</v>
+      </c>
+    </row>
+    <row r="200" ht="11" customHeight="true" outlineLevel="3">
       <c r="B200" s="15" t="s">
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>703</v>
+        <v>164</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3249,7 +2979,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>260</v>
+        <v>43</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3257,7 +2987,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>2</v>
+        <v>371</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3265,7 +2995,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>79</v>
+        <v>630</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -3273,15 +3003,15 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>496</v>
+        <v>600</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
       <c r="B205" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="16" t="n">
-        <v>1594</v>
+      <c r="C205" s="11" t="n">
+        <v>777</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3289,7 +3019,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>438</v>
+        <v>74</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3297,7 +3027,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>497</v>
+        <v>116</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3305,7 +3035,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3313,7 +3043,7 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>331</v>
+        <v>76</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3321,7 +3051,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>255</v>
+        <v>43</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3329,7 +3059,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>245</v>
+        <v>433</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3337,7 +3067,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>768</v>
+        <v>196</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3345,7 +3075,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>13</v>
+        <v>636</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3353,7 +3083,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>377</v>
+        <v>86</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3361,7 +3091,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>345</v>
+        <v>219</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3369,7 +3099,7 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>845</v>
+        <v>40</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3377,7 +3107,7 @@
         <v>216</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>764</v>
+        <v>177</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3385,7 +3115,7 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>290</v>
+        <v>268</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3393,7 +3123,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>862</v>
+        <v>81</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3401,7 +3131,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>634</v>
+        <v>471</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3409,7 +3139,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>219</v>
+        <v>336</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3417,7 +3147,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>40</v>
+        <v>685</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3425,7 +3155,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>535</v>
+        <v>254</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3433,7 +3163,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>364</v>
+        <v>725</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3441,15 +3171,15 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>373</v>
+        <v>862</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="16" t="n">
-        <v>5395</v>
+      <c r="C226" s="11" t="n">
+        <v>560</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3457,7 +3187,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>123</v>
+        <v>47</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3465,15 +3195,15 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>8</v>
+        <v>436</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="11" t="n">
-        <v>981</v>
+      <c r="C229" s="16" t="n">
+        <v>1010</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3481,7 +3211,7 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>144</v>
+        <v>857</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3489,15 +3219,15 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>350</v>
+        <v>622</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="11" t="n">
-        <v>62</v>
+      <c r="C232" s="16" t="n">
+        <v>1332</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3505,15 +3235,15 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="234" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B234" s="15" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="234" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B234" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="11" t="n">
-        <v>175</v>
+      <c r="C234" s="12" t="n">
+        <v>1674</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3521,7 +3251,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>430</v>
+        <v>248</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3529,7 +3259,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3537,7 +3267,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>712</v>
+        <v>130</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3545,15 +3275,15 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="239" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B239" s="14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="239" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B239" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="12" t="n">
-        <v>21533</v>
+      <c r="C239" s="11" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3561,7 +3291,7 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>642</v>
+        <v>8</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3569,7 +3299,7 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>145</v>
+        <v>87</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3577,7 +3307,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>913</v>
+        <v>86</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3585,15 +3315,15 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>440</v>
+        <v>322</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="16" t="n">
-        <v>2628</v>
+      <c r="C244" s="11" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3601,7 +3331,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>12</v>
+        <v>208</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3609,7 +3339,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>74</v>
+        <v>159</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3617,7 +3347,7 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>374</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3625,7 +3355,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3633,39 +3363,39 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="250" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B250" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="250" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B250" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="11" t="n">
-        <v>43</v>
+      <c r="C250" s="12" t="n">
+        <v>24121</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="C251" s="11" t="n">
-        <v>792</v>
+      <c r="C251" s="16" t="n">
+        <v>1094</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
       <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="11" t="n">
-        <v>884</v>
+      <c r="C252" s="16" t="n">
+        <v>1030</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="11" t="n">
-        <v>585</v>
+      <c r="C253" s="16" t="n">
+        <v>1443</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3673,7 +3403,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>188</v>
+        <v>284</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3681,7 +3411,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>565</v>
+        <v>291</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3689,7 +3419,7 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>194</v>
+        <v>462</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3697,7 +3427,7 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>190</v>
+        <v>311</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3705,15 +3435,15 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="259" ht="11" customHeight="true" outlineLevel="3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="259" ht="22" customHeight="true" outlineLevel="3">
       <c r="B259" s="15" t="s">
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>459</v>
+        <v>424</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3721,15 +3451,15 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>895</v>
+        <v>427</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
       <c r="B261" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="16" t="n">
-        <v>1468</v>
+      <c r="C261" s="11" t="n">
+        <v>476</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3737,7 +3467,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>435</v>
+        <v>170</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3745,7 +3475,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>829</v>
+        <v>168</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3753,71 +3483,71 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="265" ht="11" customHeight="true" outlineLevel="3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="265" ht="22" customHeight="true" outlineLevel="3">
       <c r="B265" s="15" t="s">
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="266" ht="11" customHeight="true" outlineLevel="3">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="266" ht="22" customHeight="true" outlineLevel="3">
       <c r="B266" s="15" t="s">
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="267" ht="11" customHeight="true" outlineLevel="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="267" ht="22" customHeight="true" outlineLevel="3">
       <c r="B267" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="C267" s="16" t="n">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="268" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C267" s="11" t="n">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="268" ht="22" customHeight="true" outlineLevel="3">
       <c r="B268" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="C268" s="16" t="n">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="269" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C268" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="269" ht="22" customHeight="true" outlineLevel="3">
       <c r="B269" s="15" t="s">
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="270" ht="11" customHeight="true" outlineLevel="3">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="270" ht="22" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="271" ht="11" customHeight="true" outlineLevel="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="271" ht="22" customHeight="true" outlineLevel="3">
       <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="16" t="n">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="272" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C271" s="11" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="272" ht="22" customHeight="true" outlineLevel="3">
       <c r="B272" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="16" t="n">
-        <v>1242</v>
+      <c r="C272" s="11" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3825,15 +3555,15 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="274" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B274" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="274" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B274" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="12" t="n">
-        <v>2530</v>
+      <c r="C274" s="11" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3841,7 +3571,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>61</v>
+        <v>208</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3849,15 +3579,15 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>206</v>
+        <v>118</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
       <c r="B277" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="C277" s="11" t="n">
-        <v>235</v>
+      <c r="C277" s="16" t="n">
+        <v>1993</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3865,7 +3595,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>541</v>
+        <v>798</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3873,23 +3603,23 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>66</v>
+        <v>449</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
       <c r="B280" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="C280" s="11" t="n">
-        <v>94</v>
+      <c r="C280" s="16" t="n">
+        <v>1019</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
       <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="11" t="n">
-        <v>292</v>
+      <c r="C281" s="16" t="n">
+        <v>1731</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3897,31 +3627,31 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>16</v>
+        <v>815</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
       <c r="B283" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="11" t="n">
-        <v>233</v>
+      <c r="C283" s="16" t="n">
+        <v>4832</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
       <c r="B284" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="C284" s="11" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="285" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B285" s="15" t="s">
+      <c r="C284" s="16" t="n">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="285" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B285" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="C285" s="11" t="n">
-        <v>141</v>
+      <c r="C285" s="12" t="n">
+        <v>10987</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3929,7 +3659,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>257</v>
+        <v>521</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3937,15 +3667,15 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="288" ht="11" customHeight="true" outlineLevel="3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="288" ht="22" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3953,15 +3683,15 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="290" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B290" s="14" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="290" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B290" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="C290" s="12" t="n">
-        <v>16003</v>
+      <c r="C290" s="11" t="n">
+        <v>245</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -3969,7 +3699,7 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>118</v>
+        <v>310</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -3977,7 +3707,7 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>172</v>
+        <v>826</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -3985,7 +3715,7 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>79</v>
+        <v>222</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -3993,7 +3723,7 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>217</v>
+        <v>84</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
@@ -4001,7 +3731,7 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>218</v>
+        <v>171</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
@@ -4009,7 +3739,7 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>500</v>
+        <v>37</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -4017,7 +3747,7 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>254</v>
+        <v>343</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
@@ -4025,15 +3755,15 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="299" ht="22" customHeight="true" outlineLevel="3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="299" ht="11" customHeight="true" outlineLevel="3">
       <c r="B299" s="15" t="s">
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>43</v>
+        <v>329</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -4041,7 +3771,7 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -4049,7 +3779,7 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>131</v>
+        <v>321</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -4057,7 +3787,7 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>207</v>
+        <v>301</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -4065,7 +3795,7 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -4073,7 +3803,7 @@
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>101</v>
+        <v>353</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -4081,7 +3811,7 @@
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
     </row>
     <row r="306" ht="22" customHeight="true" outlineLevel="3">
@@ -4089,7 +3819,7 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="307" ht="22" customHeight="true" outlineLevel="3">
@@ -4097,23 +3827,23 @@
         <v>306</v>
       </c>
       <c r="C307" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="308" ht="22" customHeight="true" outlineLevel="3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="308" ht="11" customHeight="true" outlineLevel="3">
       <c r="B308" s="15" t="s">
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="309" ht="22" customHeight="true" outlineLevel="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="309" ht="11" customHeight="true" outlineLevel="3">
       <c r="B309" s="15" t="s">
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>87</v>
+        <v>14</v>
       </c>
     </row>
     <row r="310" ht="22" customHeight="true" outlineLevel="3">
@@ -4121,15 +3851,15 @@
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="311" ht="22" customHeight="true" outlineLevel="3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="312" ht="22" customHeight="true" outlineLevel="3">
@@ -4137,15 +3867,15 @@
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="313" ht="22" customHeight="true" outlineLevel="3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>170</v>
+        <v>49</v>
       </c>
     </row>
     <row r="314" ht="22" customHeight="true" outlineLevel="3">
@@ -4153,7 +3883,7 @@
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>82</v>
+        <v>182</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
@@ -4161,23 +3891,23 @@
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="316" ht="11" customHeight="true" outlineLevel="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="316" ht="22" customHeight="true" outlineLevel="3">
       <c r="B316" s="15" t="s">
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>67</v>
+        <v>112</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
       <c r="B317" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="C317" s="11" t="n">
-        <v>54</v>
+      <c r="C317" s="16" t="n">
+        <v>2111</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
@@ -4185,7 +3915,7 @@
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>376</v>
+        <v>609</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -4193,7 +3923,7 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>36</v>
+        <v>668</v>
       </c>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="3">
@@ -4201,31 +3931,31 @@
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>85</v>
+        <v>311</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="16" t="n">
-        <v>1736</v>
+      <c r="C321" s="11" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="16" t="n">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="323" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B323" s="15" t="s">
+      <c r="C322" s="11" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="323" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B323" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="C323" s="11" t="n">
-        <v>279</v>
+      <c r="C323" s="17" t="n">
+        <v>139</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
@@ -4233,23 +3963,23 @@
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>150</v>
+        <v>78</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="16" t="n">
-        <v>1414</v>
-      </c>
-    </row>
-    <row r="326" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B326" s="15" t="s">
+      <c r="C325" s="11" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="326" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B326" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="C326" s="11" t="n">
-        <v>151</v>
+      <c r="C326" s="12" t="n">
+        <v>18452</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
@@ -4257,7 +3987,7 @@
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -4265,207 +3995,207 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="329" ht="11" customHeight="true" outlineLevel="3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="329" ht="22" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="330" ht="11" customHeight="true" outlineLevel="3">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="330" ht="22" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="C330" s="16" t="n">
-        <v>1065</v>
+      <c r="C330" s="11" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
       <c r="B331" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="C331" s="16" t="n">
-        <v>2766</v>
-      </c>
-    </row>
-    <row r="332" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C331" s="11" t="n">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="332" ht="11" customHeight="true" outlineLevel="3">
       <c r="B332" s="15" t="s">
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="333" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B333" s="14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="333" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B333" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="17" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="334" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B334" s="18" t="s">
+      <c r="C333" s="11" t="n">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="334" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B334" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="C334" s="17" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="335" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B335" s="19" t="s">
+      <c r="C334" s="11" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="335" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B335" s="15" t="s">
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="336" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B336" s="19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="336" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B336" s="15" t="s">
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="337" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B337" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="337" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="338" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B338" s="19" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="338" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B338" s="15" t="s">
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="339" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B339" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="339" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="340" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B340" s="14" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="340" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="12" t="n">
-        <v>19230</v>
-      </c>
-    </row>
-    <row r="341" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C340" s="11" t="n">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="341" ht="22" customHeight="true" outlineLevel="3">
       <c r="B341" s="15" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="342" ht="11" customHeight="true" outlineLevel="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="342" ht="22" customHeight="true" outlineLevel="3">
       <c r="B342" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="C342" s="16" t="n">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="343" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C342" s="11" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="343" ht="22" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="C343" s="16" t="n">
-        <v>1367</v>
+      <c r="C343" s="11" t="n">
+        <v>154</v>
       </c>
     </row>
     <row r="344" ht="22" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="C344" s="16" t="n">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="345" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C344" s="11" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="345" ht="22" customHeight="true" outlineLevel="3">
       <c r="B345" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="16" t="n">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="346" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C345" s="11" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="346" ht="22" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="347" ht="11" customHeight="true" outlineLevel="3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="347" ht="22" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="348" ht="11" customHeight="true" outlineLevel="3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="348" ht="22" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="349" ht="11" customHeight="true" outlineLevel="3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="349" ht="22" customHeight="true" outlineLevel="3">
       <c r="B349" s="15" t="s">
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="350" ht="22" customHeight="true" outlineLevel="3">
       <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="351" ht="11" customHeight="true" outlineLevel="3">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="351" ht="22" customHeight="true" outlineLevel="3">
       <c r="B351" s="15" t="s">
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="352" ht="11" customHeight="true" outlineLevel="3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="352" ht="22" customHeight="true" outlineLevel="3">
       <c r="B352" s="15" t="s">
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="353" ht="11" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" ht="22" customHeight="true" outlineLevel="3">
       <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>181</v>
+        <v>6</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
@@ -4473,7 +4203,7 @@
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>135</v>
+        <v>174</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
@@ -4481,39 +4211,39 @@
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="356" ht="11" customHeight="true" outlineLevel="3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="356" ht="22" customHeight="true" outlineLevel="3">
       <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
       <c r="C356" s="11" t="n">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="357" ht="11" customHeight="true" outlineLevel="3">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="357" ht="22" customHeight="true" outlineLevel="3">
       <c r="B357" s="15" t="s">
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="358" ht="11" customHeight="true" outlineLevel="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="358" ht="22" customHeight="true" outlineLevel="3">
       <c r="B358" s="15" t="s">
         <v>357</v>
       </c>
       <c r="C358" s="11" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="359" ht="11" customHeight="true" outlineLevel="3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="359" ht="22" customHeight="true" outlineLevel="3">
       <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
       <c r="C359" s="11" t="n">
-        <v>291</v>
+        <v>254</v>
       </c>
     </row>
     <row r="360" ht="11" customHeight="true" outlineLevel="3">
@@ -4521,15 +4251,15 @@
         <v>359</v>
       </c>
       <c r="C360" s="11" t="n">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="361" ht="11" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="361" ht="22" customHeight="true" outlineLevel="3">
       <c r="B361" s="15" t="s">
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="362" ht="11" customHeight="true" outlineLevel="3">
@@ -4537,15 +4267,15 @@
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="363" ht="11" customHeight="true" outlineLevel="3">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="363" ht="22" customHeight="true" outlineLevel="3">
       <c r="B363" s="15" t="s">
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
     </row>
     <row r="364" ht="11" customHeight="true" outlineLevel="3">
@@ -4553,7 +4283,7 @@
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>431</v>
+        <v>176</v>
       </c>
     </row>
     <row r="365" ht="11" customHeight="true" outlineLevel="3">
@@ -4561,15 +4291,15 @@
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="366" ht="11" customHeight="true" outlineLevel="3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="366" ht="22" customHeight="true" outlineLevel="3">
       <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>375</v>
+        <v>4</v>
       </c>
     </row>
     <row r="367" ht="11" customHeight="true" outlineLevel="3">
@@ -4577,7 +4307,7 @@
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>168</v>
+        <v>964</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
@@ -4585,7 +4315,7 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>29</v>
+        <v>899</v>
       </c>
     </row>
     <row r="369" ht="11" customHeight="true" outlineLevel="3">
@@ -4593,7 +4323,7 @@
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>46</v>
+        <v>884</v>
       </c>
     </row>
     <row r="370" ht="22" customHeight="true" outlineLevel="3">
@@ -4601,31 +4331,31 @@
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>83</v>
+        <v>120</v>
       </c>
     </row>
     <row r="371" ht="11" customHeight="true" outlineLevel="3">
       <c r="B371" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="C371" s="11" t="n">
-        <v>49</v>
+      <c r="C371" s="16" t="n">
+        <v>1059</v>
       </c>
     </row>
     <row r="372" ht="11" customHeight="true" outlineLevel="3">
       <c r="B372" s="15" t="s">
         <v>371</v>
       </c>
-      <c r="C372" s="11" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="373" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C372" s="16" t="n">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="373" ht="11" customHeight="true" outlineLevel="3">
       <c r="B373" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="C373" s="11" t="n">
-        <v>2</v>
+      <c r="C373" s="16" t="n">
+        <v>1170</v>
       </c>
     </row>
     <row r="374" ht="11" customHeight="true" outlineLevel="3">
@@ -4633,7 +4363,7 @@
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>92</v>
+        <v>167</v>
       </c>
     </row>
     <row r="375" ht="11" customHeight="true" outlineLevel="3">
@@ -4641,7 +4371,7 @@
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="376" ht="11" customHeight="true" outlineLevel="3">
@@ -4649,719 +4379,15 @@
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>148</v>
+        <v>703</v>
       </c>
     </row>
     <row r="377" ht="11" customHeight="true" outlineLevel="3">
       <c r="B377" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="C377" s="16" t="n">
-        <v>3951</v>
-      </c>
-    </row>
-    <row r="378" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B378" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="C378" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="379" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B379" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="C379" s="16" t="n">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="380" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B380" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="C380" s="16" t="n">
-        <v>1523</v>
-      </c>
-    </row>
-    <row r="381" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B381" s="15" t="s">
-        <v>380</v>
-      </c>
-      <c r="C381" s="11" t="n">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="382" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B382" s="15" t="s">
-        <v>381</v>
-      </c>
-      <c r="C382" s="11" t="n">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="383" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B383" s="15" t="s">
-        <v>382</v>
-      </c>
-      <c r="C383" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="384" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B384" s="15" t="s">
-        <v>383</v>
-      </c>
-      <c r="C384" s="11" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="385" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B385" s="14" t="s">
-        <v>384</v>
-      </c>
-      <c r="C385" s="17" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="386" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B386" s="15" t="s">
-        <v>385</v>
-      </c>
-      <c r="C386" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="387" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B387" s="15" t="s">
-        <v>386</v>
-      </c>
-      <c r="C387" s="11" t="n">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="388" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B388" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="C388" s="12" t="n">
-        <v>36545</v>
-      </c>
-    </row>
-    <row r="389" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B389" s="15" t="s">
-        <v>388</v>
-      </c>
-      <c r="C389" s="11" t="n">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="390" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B390" s="15" t="s">
-        <v>389</v>
-      </c>
-      <c r="C390" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="391" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B391" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="C391" s="11" t="n">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="392" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B392" s="15" t="s">
-        <v>391</v>
-      </c>
-      <c r="C392" s="11" t="n">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="393" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B393" s="15" t="s">
-        <v>392</v>
-      </c>
-      <c r="C393" s="11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="394" ht="33" customHeight="true" outlineLevel="3">
-      <c r="B394" s="15" t="s">
-        <v>393</v>
-      </c>
-      <c r="C394" s="16" t="n">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="395" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B395" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="C395" s="11" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="396" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B396" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="C396" s="11" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="397" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B397" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="C397" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="398" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B398" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="C398" s="11" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="399" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B399" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="C399" s="11" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="400" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B400" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="C400" s="11" t="n">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="401" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B401" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="C401" s="11" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="402" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B402" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="C402" s="11" t="n">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="403" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B403" s="15" t="s">
-        <v>402</v>
-      </c>
-      <c r="C403" s="11" t="n">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="404" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B404" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="C404" s="11" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="405" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B405" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="C405" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="406" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B406" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="C406" s="11" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="407" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B407" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="C407" s="11" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="408" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B408" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="C408" s="11" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="409" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B409" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="C409" s="16" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="410" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B410" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="C410" s="11" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="411" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B411" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="C411" s="11" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="412" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B412" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="C412" s="11" t="n">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="413" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B413" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="C413" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="414" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B414" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="C414" s="16" t="n">
-        <v>1461</v>
-      </c>
-    </row>
-    <row r="415" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B415" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="C415" s="11" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="416" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B416" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="C416" s="11" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="417" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B417" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="C417" s="16" t="n">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="418" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B418" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="C418" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="419" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B419" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="C419" s="11" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="420" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B420" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="C420" s="11" t="n">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="421" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B421" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="C421" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="422" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B422" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="C422" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="423" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B423" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="C423" s="11" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="424" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B424" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="C424" s="11" t="n">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="425" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B425" s="15" t="s">
-        <v>424</v>
-      </c>
-      <c r="C425" s="11" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="426" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B426" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="C426" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="427" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B427" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="C427" s="11" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="428" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B428" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="C428" s="11" t="n">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="429" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B429" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="C429" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="430" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B430" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="C430" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="431" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B431" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="C431" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="432" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B432" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="C432" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="433" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B433" s="15" t="s">
-        <v>432</v>
-      </c>
-      <c r="C433" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="434" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B434" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="C434" s="11" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="435" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B435" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="C435" s="11" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="436" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B436" s="15" t="s">
-        <v>435</v>
-      </c>
-      <c r="C436" s="11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="437" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B437" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="C437" s="11" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="438" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B438" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="C438" s="11" t="n">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="439" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B439" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="C439" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="440" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B440" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="C440" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="441" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B441" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="C441" s="11" t="n">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="442" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B442" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="C442" s="11" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="443" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B443" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="C443" s="16" t="n">
-        <v>2523</v>
-      </c>
-    </row>
-    <row r="444" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B444" s="15" t="s">
-        <v>443</v>
-      </c>
-      <c r="C444" s="16" t="n">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="445" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B445" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="C445" s="11" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="446" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B446" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="C446" s="16" t="n">
-        <v>3148</v>
-      </c>
-    </row>
-    <row r="447" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B447" s="15" t="s">
-        <v>446</v>
-      </c>
-      <c r="C447" s="16" t="n">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="448" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B448" s="15" t="s">
-        <v>447</v>
-      </c>
-      <c r="C448" s="11" t="n">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="449" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B449" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="C449" s="16" t="n">
-        <v>2295</v>
-      </c>
-    </row>
-    <row r="450" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B450" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="C450" s="11" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="451" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B451" s="15" t="s">
-        <v>450</v>
-      </c>
-      <c r="C451" s="11" t="n">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="452" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B452" s="15" t="s">
-        <v>451</v>
-      </c>
-      <c r="C452" s="11" t="n">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="453" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B453" s="15" t="s">
-        <v>452</v>
-      </c>
-      <c r="C453" s="16" t="n">
-        <v>3390</v>
-      </c>
-    </row>
-    <row r="454" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B454" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="C454" s="11" t="n">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="455" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B455" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="C455" s="16" t="n">
-        <v>3226</v>
-      </c>
-    </row>
-    <row r="456" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B456" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="C456" s="11" t="n">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="457" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B457" s="15" t="s">
-        <v>456</v>
-      </c>
-      <c r="C457" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="458" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B458" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="C458" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="459" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B459" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="C459" s="11" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="460" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B460" s="15" t="s">
-        <v>459</v>
-      </c>
-      <c r="C460" s="11" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="461" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B461" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="C461" s="11" t="n">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="462" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B462" s="15" t="s">
-        <v>461</v>
-      </c>
-      <c r="C462" s="11" t="n">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="463" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B463" s="18" t="s">
-        <v>462</v>
-      </c>
-      <c r="C463" s="17" t="n">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="464" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B464" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="C464" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="465" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B465" s="19" t="s">
-        <v>464</v>
-      </c>
-      <c r="C465" s="11" t="n">
-        <v>312</v>
+      <c r="C377" s="11" t="n">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
